--- a/Sim/Scenario_H2_Figures/energy_mix_2050.xlsx
+++ b/Sim/Scenario_H2_Figures/energy_mix_2050.xlsx
@@ -480,22 +480,22 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>-2.780867894241443E-06</v>
+        <v>-1.413267671059892E-06</v>
       </c>
       <c r="D2">
-        <v>-5.294498822984311E-06</v>
+        <v>-5.261140786199643E-06</v>
       </c>
       <c r="E2">
-        <v>1.345821433581716E-08</v>
+        <v>1.503056987148642E-08</v>
       </c>
       <c r="F2">
-        <v>1.008252325275044E-08</v>
+        <v>1.043524674257652E-08</v>
       </c>
       <c r="G2">
-        <v>1.538561856975536E-08</v>
+        <v>1.50410171596366E-08</v>
       </c>
       <c r="H2">
-        <v>2.26901230628134E-09</v>
+        <v>2.880192736389882E-09</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -506,22 +506,22 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>881.140528</v>
+        <v>386.6019542</v>
       </c>
       <c r="D3">
-        <v>799.160488</v>
+        <v>352.5496074</v>
       </c>
       <c r="E3">
-        <v>725.614209</v>
+        <v>315.9652707</v>
       </c>
       <c r="F3">
-        <v>636.4773280000001</v>
+        <v>279.277778</v>
       </c>
       <c r="G3">
-        <v>553.600629</v>
+        <v>245.4887104</v>
       </c>
       <c r="H3">
-        <v>456.125046</v>
+        <v>202.6002283</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -558,22 +558,22 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>382.7989705517364</v>
+        <v>567.4112187736565</v>
       </c>
       <c r="D5">
-        <v>346.5772754618549</v>
+        <v>516.5288750298665</v>
       </c>
       <c r="E5">
-        <v>310.8810070062583</v>
+        <v>457.3366950650386</v>
       </c>
       <c r="F5">
-        <v>269.4368818429967</v>
+        <v>399.4098516317432</v>
       </c>
       <c r="G5">
-        <v>232.5618881899655</v>
+        <v>348.4029124527975</v>
       </c>
       <c r="H5">
-        <v>190.1599798401071</v>
+        <v>285.3536430549241</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -610,22 +610,22 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>4056.429403720711</v>
+        <v>3561.919369934635</v>
       </c>
       <c r="D7">
-        <v>4320.462396910774</v>
+        <v>3873.988683445496</v>
       </c>
       <c r="E7">
-        <v>4864.135886199702</v>
+        <v>4454.662337642075</v>
       </c>
       <c r="F7">
-        <v>3412.624410560908</v>
+        <v>3055.524264681851</v>
       </c>
       <c r="G7">
-        <v>7.334936428879504E-08</v>
+        <v>7.304005977451926E-08</v>
       </c>
       <c r="H7">
-        <v>2.09300212303262E-08</v>
+        <v>2.296507732468084E-08</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -662,22 +662,22 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>-1.659268212363069E-05</v>
+        <v>-8.443495490654625E-06</v>
       </c>
       <c r="D9">
-        <v>-3.141685041357826E-05</v>
+        <v>-3.121931005443707E-05</v>
       </c>
       <c r="E9">
-        <v>2.321274900516301E-09</v>
+        <v>2.996433416868206E-09</v>
       </c>
       <c r="F9">
-        <v>-2.177699168950879E-09</v>
+        <v>-1.837223511912574E-09</v>
       </c>
       <c r="G9">
-        <v>1.523509379792579E-08</v>
+        <v>1.514637348202126E-08</v>
       </c>
       <c r="H9">
-        <v>6.812080118052184E-10</v>
+        <v>1.288002198508487E-09</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -688,22 +688,22 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <v>18391.3279833952</v>
+        <v>18667.83748154312</v>
       </c>
       <c r="D10">
-        <v>16546.9699430124</v>
+        <v>16888.06890166814</v>
       </c>
       <c r="E10">
-        <v>14801.81152789121</v>
+        <v>14847.93055377572</v>
       </c>
       <c r="F10">
-        <v>12738.1646836911</v>
+        <v>12842.55165138194</v>
       </c>
       <c r="G10">
-        <v>10866.36102023677</v>
+        <v>11061.8916362232</v>
       </c>
       <c r="H10">
-        <v>8692.235542588889</v>
+        <v>8849.611150727011</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -714,22 +714,22 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>584.6400101264977</v>
+        <v>584.640005152268</v>
       </c>
       <c r="D11">
-        <v>584.6400191855148</v>
+        <v>584.6400190648567</v>
       </c>
       <c r="E11">
-        <v>584.6399999947134</v>
+        <v>584.6399999941248</v>
       </c>
       <c r="F11">
-        <v>906.3563707508486</v>
+        <v>906.3563707505785</v>
       </c>
       <c r="G11">
-        <v>1370.56754697254</v>
+        <v>1370.567546977016</v>
       </c>
       <c r="H11">
-        <v>1514.04469908388</v>
+        <v>1514.044699053134</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -740,22 +740,22 @@
         <v>22</v>
       </c>
       <c r="C12">
-        <v>3787.200011291854</v>
+        <v>3787.200005745454</v>
       </c>
       <c r="D12">
-        <v>3787.200021400053</v>
+        <v>3787.20002126546</v>
       </c>
       <c r="E12">
-        <v>3787.199999992451</v>
+        <v>3787.199999991642</v>
       </c>
       <c r="F12">
-        <v>5884.933078751146</v>
+        <v>5884.933078750776</v>
       </c>
       <c r="G12">
-        <v>10218.692263182</v>
+        <v>9910.711625415814</v>
       </c>
       <c r="H12">
-        <v>11860.77942360583</v>
+        <v>11607.13722875789</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -766,22 +766,22 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>-8.650490492691666E-06</v>
+        <v>-6.258939557574998E-06</v>
       </c>
       <c r="D13">
-        <v>-2.176225133618739E-05</v>
+        <v>-1.652432463801645E-05</v>
       </c>
       <c r="E13">
-        <v>5.631307639427836E-09</v>
+        <v>5.424307039936845E-09</v>
       </c>
       <c r="F13">
-        <v>2.920866899963446E-08</v>
+        <v>2.863248826521865E-08</v>
       </c>
       <c r="G13">
-        <v>2.71609875073041E-08</v>
+        <v>1.422512809990759E-08</v>
       </c>
       <c r="H13">
-        <v>1.670932350342272E-08</v>
+        <v>9.440687807936425E-09</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -792,22 +792,22 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>4264.68291</v>
+        <v>1861.515983</v>
       </c>
       <c r="D14">
-        <v>3862.801931</v>
+        <v>1696.344255</v>
       </c>
       <c r="E14">
-        <v>3489.92828</v>
+        <v>1535.329537</v>
       </c>
       <c r="F14">
-        <v>3064.882875</v>
+        <v>1349.914163</v>
       </c>
       <c r="G14">
-        <v>2675.370736</v>
+        <v>1186.924653</v>
       </c>
       <c r="H14">
-        <v>2203.802436</v>
+        <v>977.969483</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -844,22 +844,22 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>1852.730837223593</v>
+        <v>2732.125494241667</v>
       </c>
       <c r="D16">
-        <v>1675.207169051791</v>
+        <v>2485.354598922363</v>
       </c>
       <c r="E16">
-        <v>1495.219359821045</v>
+        <v>2222.277569087904</v>
       </c>
       <c r="F16">
-        <v>1297.442099399978</v>
+        <v>1930.583310763862</v>
       </c>
       <c r="G16">
-        <v>1123.895510973524</v>
+        <v>1684.509276050835</v>
       </c>
       <c r="H16">
-        <v>918.7722373822547</v>
+        <v>1377.427637499728</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -896,22 +896,22 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>9027.676882905553</v>
+        <v>6625.975265705849</v>
       </c>
       <c r="D18">
-        <v>8961.095156429083</v>
+        <v>6793.87755011139</v>
       </c>
       <c r="E18">
-        <v>9193.017739960535</v>
+        <v>7238.196258777018</v>
       </c>
       <c r="F18">
-        <v>8198.109139580734</v>
+        <v>6483.517716107741</v>
       </c>
       <c r="G18">
-        <v>2336.666577823422</v>
+        <v>1253.320873218236</v>
       </c>
       <c r="H18">
-        <v>984.6403302903286</v>
+        <v>254.6640595561414</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -948,22 +948,22 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>-4.839215892064286E-05</v>
+        <v>-3.503140001547117E-05</v>
       </c>
       <c r="D20">
-        <v>-0.000121555142671309</v>
+        <v>-9.21480933506297E-05</v>
       </c>
       <c r="E20">
-        <v>-2.248228020674723E-09</v>
+        <v>-2.382148672011229E-09</v>
       </c>
       <c r="F20">
-        <v>1.155360734496401E-08</v>
+        <v>1.120677140000807E-08</v>
       </c>
       <c r="G20">
-        <v>9.044460040470224E-09</v>
+        <v>3.4772266627194E-09</v>
       </c>
       <c r="H20">
-        <v>7.453548601554706E-09</v>
+        <v>2.491045742083366E-09</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -974,22 +974,22 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>19738.68879467133</v>
+        <v>20845.11635987293</v>
       </c>
       <c r="D21">
-        <v>17741.31588738424</v>
+        <v>18855.56629461462</v>
       </c>
       <c r="E21">
-        <v>15785.38961114271</v>
+        <v>16764.69316740531</v>
       </c>
       <c r="F21">
-        <v>13605.50927961706</v>
+        <v>14432.60584113245</v>
       </c>
       <c r="G21">
-        <v>11659.61461526722</v>
+        <v>12452.10565041259</v>
       </c>
       <c r="H21">
-        <v>9337.29641566652</v>
+        <v>9969.479058538407</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1000,22 +1000,22 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>389.7600293595265</v>
+        <v>389.7600212523246</v>
       </c>
       <c r="D22">
-        <v>389.76007376184</v>
+        <v>389.7600559271074</v>
       </c>
       <c r="E22">
-        <v>389.7599999986975</v>
+        <v>389.7599999988142</v>
       </c>
       <c r="F22">
-        <v>604.2375804894782</v>
+        <v>604.2375804897532</v>
       </c>
       <c r="G22">
-        <v>913.7116987047397</v>
+        <v>913.7116984925439</v>
       </c>
       <c r="H22">
-        <v>1009.363132506772</v>
+        <v>1009.363132648104</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1026,22 +1026,22 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>2524.800034934842</v>
+        <v>2524.800025287787</v>
       </c>
       <c r="D23">
-        <v>2524.800087774101</v>
+        <v>2524.800066556674</v>
       </c>
       <c r="E23">
-        <v>2524.799999997923</v>
+        <v>2524.799999998083</v>
       </c>
       <c r="F23">
-        <v>3923.28871915214</v>
+        <v>3923.288719152517</v>
       </c>
       <c r="G23">
-        <v>10541.62226275374</v>
+        <v>10135.51951297907</v>
       </c>
       <c r="H23">
-        <v>13194.55008110353</v>
+        <v>12698.23285423542</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1338,22 +1338,22 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>-6.026168145650603E-06</v>
+        <v>-6.073786120127589E-06</v>
       </c>
       <c r="D35">
-        <v>-1.438458788737826E-05</v>
+        <v>-2.81053820272676E-05</v>
       </c>
       <c r="E35">
-        <v>1.51898629708161E-08</v>
+        <v>1.424310462652971E-08</v>
       </c>
       <c r="F35">
-        <v>8.985161640506476E-09</v>
+        <v>4.213415075559838E-09</v>
       </c>
       <c r="G35">
-        <v>5.233163083494028E-08</v>
+        <v>1.09194883308975E-08</v>
       </c>
       <c r="H35">
-        <v>9.732948854874921E-09</v>
+        <v>1.02089183084598E-08</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1364,22 +1364,22 @@
         <v>13</v>
       </c>
       <c r="C36">
-        <v>11346.48571</v>
+        <v>4970.39329</v>
       </c>
       <c r="D36">
-        <v>10312.17593</v>
+        <v>4519.3539</v>
       </c>
       <c r="E36">
-        <v>9311.11802</v>
+        <v>4093.526394</v>
       </c>
       <c r="F36">
-        <v>8170.54772</v>
+        <v>3603.343382</v>
       </c>
       <c r="G36">
-        <v>7128.92508</v>
+        <v>3150.283235</v>
       </c>
       <c r="H36">
-        <v>5865.19856</v>
+        <v>2597.017379</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1416,22 +1416,22 @@
         <v>15</v>
       </c>
       <c r="C38">
-        <v>4929.319365046701</v>
+        <v>7294.988787433093</v>
       </c>
       <c r="D38">
-        <v>4472.150323983335</v>
+        <v>6621.413692496917</v>
       </c>
       <c r="E38">
-        <v>3989.240701632126</v>
+        <v>5925.081039141192</v>
       </c>
       <c r="F38">
-        <v>3458.798616620409</v>
+        <v>5153.331088001533</v>
       </c>
       <c r="G38">
-        <v>2994.787543588797</v>
+        <v>4470.950491354453</v>
       </c>
       <c r="H38">
-        <v>2445.219892135334</v>
+        <v>3657.786435169183</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1468,22 +1468,22 @@
         <v>17</v>
       </c>
       <c r="C40">
-        <v>14516.29453215309</v>
+        <v>8140.202133735163</v>
       </c>
       <c r="D40">
-        <v>13828.52385167988</v>
+        <v>8035.701807912356</v>
       </c>
       <c r="E40">
-        <v>13445.29877552367</v>
+        <v>8227.707149514094</v>
       </c>
       <c r="F40">
-        <v>10942.91627278888</v>
+        <v>6375.711934783879</v>
       </c>
       <c r="G40">
-        <v>1600.978166131761</v>
+        <v>4.597858821994212E-08</v>
       </c>
       <c r="H40">
-        <v>4.300047299609434E-08</v>
+        <v>5.388263916527091E-08</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1520,22 +1520,22 @@
         <v>19</v>
       </c>
       <c r="C42">
-        <v>-3.590530509919666E-05</v>
+        <v>-3.620328523157505E-05</v>
       </c>
       <c r="D42">
-        <v>-8.551751927474433E-05</v>
+        <v>-0.0001666050606222655</v>
       </c>
       <c r="E42">
-        <v>3.397090284934484E-09</v>
+        <v>2.803592454537809E-09</v>
       </c>
       <c r="F42">
-        <v>-1.626288069734462E-09</v>
+        <v>-5.070283234420597E-09</v>
       </c>
       <c r="G42">
-        <v>2.737771873457214E-08</v>
+        <v>7.261990511168239E-09</v>
       </c>
       <c r="H42">
-        <v>7.230798631827942E-09</v>
+        <v>1.04238543912651E-08</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1546,22 +1546,22 @@
         <v>20</v>
       </c>
       <c r="C43">
-        <v>29955.98782446782</v>
+        <v>33109.7887560148</v>
       </c>
       <c r="D43">
-        <v>27080.01234335905</v>
+        <v>29945.31074457024</v>
       </c>
       <c r="E43">
-        <v>24133.59507798991</v>
+        <v>26714.36777682438</v>
       </c>
       <c r="F43">
-        <v>20856.18499546033</v>
+        <v>23115.25722093949</v>
       </c>
       <c r="G43">
-        <v>17945.33415696207</v>
+        <v>19913.28624516303</v>
       </c>
       <c r="H43">
-        <v>14467.72219812411</v>
+        <v>16084.25976537438</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1572,22 +1572,22 @@
         <v>21</v>
       </c>
       <c r="C44">
-        <v>584.6400219163739</v>
+        <v>584.6400220973983</v>
       </c>
       <c r="D44">
-        <v>584.6400522145829</v>
+        <v>584.6401017525897</v>
       </c>
       <c r="E44">
-        <v>584.6399999937754</v>
+        <v>584.6399999942929</v>
       </c>
       <c r="F44">
-        <v>906.3563707504112</v>
+        <v>906.3563707531428</v>
       </c>
       <c r="G44">
-        <v>1370.567547885189</v>
+        <v>1370.567547367587</v>
       </c>
       <c r="H44">
-        <v>1514.044698750154</v>
+        <v>1514.044698585271</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1598,22 +1598,22 @@
         <v>22</v>
       </c>
       <c r="C45">
-        <v>3787.200024438956</v>
+        <v>3787.200024640201</v>
       </c>
       <c r="D45">
-        <v>3787.200058232358</v>
+        <v>3787.200113498285</v>
       </c>
       <c r="E45">
-        <v>3787.199999991163</v>
+        <v>3787.199999991873</v>
       </c>
       <c r="F45">
-        <v>5884.933078750547</v>
+        <v>5884.933078754291</v>
       </c>
       <c r="G45">
-        <v>15189.75288220805</v>
+        <v>12812.0892038922</v>
       </c>
       <c r="H45">
-        <v>17267.1174924243</v>
+        <v>13998.93631158688</v>
       </c>
     </row>
   </sheetData>
@@ -1660,22 +1660,22 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>-3.918914715452391E-06</v>
+        <v>-1.640980225783539E-06</v>
       </c>
       <c r="D2">
-        <v>-5.314968752036851E-06</v>
+        <v>-5.270478021991066E-06</v>
       </c>
       <c r="E2">
-        <v>1.352214823024524E-08</v>
+        <v>1.413791134703524E-08</v>
       </c>
       <c r="F2">
-        <v>9.340679570328124E-09</v>
+        <v>1.053900648162769E-08</v>
       </c>
       <c r="G2">
-        <v>1.440541339925033E-08</v>
+        <v>1.649547877651846E-08</v>
       </c>
       <c r="H2">
-        <v>1.840972553206379E-09</v>
+        <v>2.72201468929316E-09</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1686,22 +1686,22 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>1194.786525</v>
+        <v>523.448443</v>
       </c>
       <c r="D3">
-        <v>1082.559141</v>
+        <v>476.273419</v>
       </c>
       <c r="E3">
-        <v>977.0127660000001</v>
+        <v>428.597846</v>
       </c>
       <c r="F3">
-        <v>854.085331</v>
+        <v>377.7961098</v>
       </c>
       <c r="G3">
-        <v>749.869243</v>
+        <v>331.5295404</v>
       </c>
       <c r="H3">
-        <v>614.9359470000001</v>
+        <v>273.3161763</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1738,22 +1738,22 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>530.7699634494818</v>
+        <v>785.5941187471233</v>
       </c>
       <c r="D5">
-        <v>480.0739597766371</v>
+        <v>713.5446440627372</v>
       </c>
       <c r="E5">
-        <v>428.0348074904538</v>
+        <v>634.361945872558</v>
       </c>
       <c r="F5">
-        <v>369.7139208547028</v>
+        <v>552.4974917959509</v>
       </c>
       <c r="G5">
-        <v>322.1201913111767</v>
+        <v>481.1305452674981</v>
       </c>
       <c r="H5">
-        <v>262.1534156005743</v>
+        <v>393.6400364571189</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1790,22 +1790,22 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>4370.25619883557</v>
+        <v>3698.774387582798</v>
       </c>
       <c r="D7">
-        <v>4603.964709032536</v>
+        <v>3997.553008085183</v>
       </c>
       <c r="E7">
-        <v>5115.551931826495</v>
+        <v>4567.142738239808</v>
       </c>
       <c r="F7">
-        <v>3630.23115368075</v>
+        <v>3153.919801830441</v>
       </c>
       <c r="G7">
-        <v>6.89971251840593E-08</v>
+        <v>7.828166518555951E-08</v>
       </c>
       <c r="H7">
-        <v>1.957307677254846E-08</v>
+        <v>2.242133790685508E-08</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1842,22 +1842,22 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>-2.337394169229186E-05</v>
+        <v>-9.800319050492866E-06</v>
       </c>
       <c r="D9">
-        <v>-3.153806807192902E-05</v>
+        <v>-3.127460376925486E-05</v>
       </c>
       <c r="E9">
-        <v>2.360331339616589E-09</v>
+        <v>2.592007613382317E-09</v>
       </c>
       <c r="F9">
-        <v>-2.712795199602353E-09</v>
+        <v>-1.860303418793986E-09</v>
       </c>
       <c r="G9">
-        <v>1.398670587034479E-08</v>
+        <v>1.664986553849971E-08</v>
       </c>
       <c r="H9">
-        <v>2.766068752139299E-10</v>
+        <v>1.125875012521519E-09</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1868,22 +1868,22 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <v>18005.88091969838</v>
+        <v>18335.9954207206</v>
       </c>
       <c r="D10">
-        <v>16184.57277852132</v>
+        <v>16549.85605410693</v>
       </c>
       <c r="E10">
-        <v>14383.97094534793</v>
+        <v>14616.6666974761</v>
       </c>
       <c r="F10">
-        <v>12332.86964711513</v>
+        <v>12607.20769513148</v>
       </c>
       <c r="G10">
-        <v>10631.18327184962</v>
+        <v>10841.28540668941</v>
       </c>
       <c r="H10">
-        <v>8461.220403785177</v>
+        <v>8665.725768320875</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1894,22 +1894,22 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>584.640014265755</v>
+        <v>584.640005980471</v>
       </c>
       <c r="D11">
-        <v>584.6400192595548</v>
+        <v>584.6400190986302</v>
       </c>
       <c r="E11">
-        <v>584.6399999946793</v>
+        <v>584.6399999944773</v>
       </c>
       <c r="F11">
-        <v>906.3563707512729</v>
+        <v>906.3563707505969</v>
       </c>
       <c r="G11">
-        <v>1370.567547035516</v>
+        <v>1370.567546901171</v>
       </c>
       <c r="H11">
-        <v>1514.04469910438</v>
+        <v>1514.044699061349</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1920,22 +1920,22 @@
         <v>22</v>
       </c>
       <c r="C12">
-        <v>3787.200015907241</v>
+        <v>3787.200006668925</v>
       </c>
       <c r="D12">
-        <v>3787.200021482644</v>
+        <v>3787.200021303134</v>
       </c>
       <c r="E12">
-        <v>3787.199999992405</v>
+        <v>3787.199999992127</v>
       </c>
       <c r="F12">
-        <v>5884.933078751728</v>
+        <v>5884.933078750801</v>
       </c>
       <c r="G12">
-        <v>10415.03456075892</v>
+        <v>9996.710388403098</v>
       </c>
       <c r="H12">
-        <v>12019.71217231265</v>
+        <v>11678.04859788679</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1946,22 +1946,22 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>-8.654965131697565E-06</v>
+        <v>-6.259018479806362E-06</v>
       </c>
       <c r="D13">
-        <v>-2.150518189143608E-05</v>
+        <v>-1.655118934292899E-05</v>
       </c>
       <c r="E13">
-        <v>5.62989989618162E-09</v>
+        <v>5.424761216440776E-09</v>
       </c>
       <c r="F13">
-        <v>2.920885049821609E-08</v>
+        <v>2.863300871538147E-08</v>
       </c>
       <c r="G13">
-        <v>2.736079678687312E-08</v>
+        <v>1.438201414250276E-08</v>
       </c>
       <c r="H13">
-        <v>1.681903255678553E-08</v>
+        <v>1.14320497458269E-08</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1972,22 +1972,22 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>4226.78714</v>
+        <v>1859.783982</v>
       </c>
       <c r="D14">
-        <v>3867.937906</v>
+        <v>1692.681605</v>
       </c>
       <c r="E14">
-        <v>3481.146039</v>
+        <v>1536.36399</v>
       </c>
       <c r="F14">
-        <v>3064.287687</v>
+        <v>1350.695672</v>
       </c>
       <c r="G14">
-        <v>2668.635776</v>
+        <v>1182.874058</v>
       </c>
       <c r="H14">
-        <v>2202.698583</v>
+        <v>975.8158560000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2024,22 +2024,22 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>1877.700835619415</v>
+        <v>2791.173394272374</v>
       </c>
       <c r="D16">
-        <v>1715.283902832843</v>
+        <v>2535.946468001199</v>
       </c>
       <c r="E16">
-        <v>1525.109727832302</v>
+        <v>2273.951798989593</v>
       </c>
       <c r="F16">
-        <v>1326.459749044099</v>
+        <v>1975.28761337478</v>
       </c>
       <c r="G16">
-        <v>1146.361812149682</v>
+        <v>1716.63988936359</v>
       </c>
       <c r="H16">
-        <v>939.0326883135338</v>
+        <v>1405.40598530044</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2076,22 +2076,22 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>8993.437493363954</v>
+        <v>6624.624751232059</v>
       </c>
       <c r="D18">
-        <v>8965.736055469382</v>
+        <v>6791.020501990148</v>
       </c>
       <c r="E18">
-        <v>9185.076547213774</v>
+        <v>7239.005375697759</v>
       </c>
       <c r="F18">
-        <v>8197.570586497741</v>
+        <v>6484.13060553218</v>
       </c>
       <c r="G18">
-        <v>2331.10359867844</v>
+        <v>1248.633133444357</v>
       </c>
       <c r="H18">
-        <v>983.3451865976632</v>
+        <v>255.2443018516469</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2128,22 +2128,22 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>-4.841744019788394E-05</v>
+        <v>-3.503185254214577E-05</v>
       </c>
       <c r="D20">
-        <v>-0.0001201183741375288</v>
+        <v>-9.229750257821106E-05</v>
       </c>
       <c r="E20">
-        <v>-2.24908530259042E-09</v>
+        <v>-2.381890448205708E-09</v>
       </c>
       <c r="F20">
-        <v>1.155370724244699E-08</v>
+        <v>1.120707429721422E-08</v>
       </c>
       <c r="G20">
-        <v>9.1491773615359E-09</v>
+        <v>3.629190686412829E-09</v>
       </c>
       <c r="H20">
-        <v>7.540235236910763E-09</v>
+        <v>4.862691232178162E-09</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2154,22 +2154,22 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>18919.48404079659</v>
+        <v>20173.13267893143</v>
       </c>
       <c r="D21">
-        <v>17191.88535167926</v>
+        <v>18224.09478847815</v>
       </c>
       <c r="E21">
-        <v>15233.46555429299</v>
+        <v>16252.73888600253</v>
       </c>
       <c r="F21">
-        <v>13163.00646611997</v>
+        <v>13991.04655960036</v>
       </c>
       <c r="G21">
-        <v>11251.7041473306</v>
+        <v>12018.81996466596</v>
       </c>
       <c r="H21">
-        <v>9031.219206338334</v>
+        <v>9635.742157827219</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2180,22 +2180,22 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>389.7600293748483</v>
+        <v>389.7600212525984</v>
       </c>
       <c r="D22">
-        <v>389.760072890036</v>
+        <v>389.760056017814</v>
       </c>
       <c r="E22">
-        <v>389.7599999986982</v>
+        <v>389.759999998814</v>
       </c>
       <c r="F22">
-        <v>604.2375804894781</v>
+        <v>604.2375804897531</v>
       </c>
       <c r="G22">
-        <v>913.7116987085521</v>
+        <v>913.711698484318</v>
       </c>
       <c r="H22">
-        <v>1009.363132502423</v>
+        <v>1009.363132527025</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2206,22 +2206,22 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>2524.800034953064</v>
+        <v>2524.800025288113</v>
       </c>
       <c r="D23">
-        <v>2524.800086736723</v>
+        <v>2524.800066664632</v>
       </c>
       <c r="E23">
-        <v>2524.799999997924</v>
+        <v>2524.799999998083</v>
       </c>
       <c r="F23">
-        <v>3923.28871915214</v>
+        <v>3923.288719152517</v>
       </c>
       <c r="G23">
-        <v>10541.08852942437</v>
+        <v>10137.02531561478</v>
       </c>
       <c r="H23">
-        <v>13194.84556147744</v>
+        <v>12695.9580573864</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2232,22 +2232,22 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>-2.097319032140577E-06</v>
+        <v>-1.869165823934269E-06</v>
       </c>
       <c r="D24">
-        <v>-5.281025616608995E-06</v>
+        <v>-5.275782830318562E-06</v>
       </c>
       <c r="E24">
-        <v>1.341955934099337E-08</v>
+        <v>1.383474209277333E-08</v>
       </c>
       <c r="F24">
-        <v>1.03539094939966E-08</v>
+        <v>1.009001403729546E-08</v>
       </c>
       <c r="G24">
-        <v>1.557020955312216E-08</v>
+        <v>1.607862375655017E-08</v>
       </c>
       <c r="H24">
-        <v>2.200289232152528E-09</v>
+        <v>2.498335902717022E-09</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2258,22 +2258,22 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <v>120.6513418</v>
+        <v>52.8520137</v>
       </c>
       <c r="D25">
-        <v>125.5564722</v>
+        <v>55.0256454</v>
       </c>
       <c r="E25">
-        <v>135.6063814</v>
+        <v>59.6177927</v>
       </c>
       <c r="F25">
-        <v>152.8760764</v>
+        <v>67.42081659999999</v>
       </c>
       <c r="G25">
-        <v>176.8312405</v>
+        <v>78.1420042</v>
       </c>
       <c r="H25">
-        <v>207.6589155</v>
+        <v>91.94809069999999</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2310,22 +2310,22 @@
         <v>15</v>
       </c>
       <c r="C27">
-        <v>53.59794983685079</v>
+        <v>79.32057419070449</v>
       </c>
       <c r="D27">
-        <v>55.67953801658796</v>
+        <v>82.43847599374837</v>
       </c>
       <c r="E27">
-        <v>59.40992089427064</v>
+        <v>88.23949748905089</v>
       </c>
       <c r="F27">
-        <v>66.1765422992585</v>
+        <v>98.59771344363581</v>
       </c>
       <c r="G27">
-        <v>75.96112692231512</v>
+        <v>113.4031827524768</v>
       </c>
       <c r="H27">
-        <v>88.52709631785685</v>
+        <v>132.4270322623713</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2362,22 +2362,22 @@
         <v>17</v>
       </c>
       <c r="C29">
-        <v>3837.844030441635</v>
+        <v>3770.044693702734</v>
       </c>
       <c r="D29">
-        <v>4138.921800423951</v>
+        <v>4068.3909738225</v>
       </c>
       <c r="E29">
-        <v>4715.635047019889</v>
+        <v>4639.646458318264</v>
       </c>
       <c r="F29">
-        <v>3313.975889129782</v>
+        <v>3228.520629330613</v>
       </c>
       <c r="G29">
-        <v>7.415901602036492E-08</v>
+        <v>7.642422637375827E-08</v>
       </c>
       <c r="H29">
-        <v>2.071853387964956E-08</v>
+        <v>2.168061290494326E-08</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2414,22 +2414,22 @@
         <v>19</v>
       </c>
       <c r="C31">
-        <v>-1.251958980943204E-05</v>
+        <v>-1.116005102035507E-05</v>
       </c>
       <c r="D31">
-        <v>-3.133706468693977E-05</v>
+        <v>-3.130601792548395E-05</v>
       </c>
       <c r="E31">
-        <v>2.297699094495016E-09</v>
+        <v>2.402992479969999E-09</v>
       </c>
       <c r="F31">
-        <v>-1.974988995316023E-09</v>
+        <v>-2.059055854817659E-09</v>
       </c>
       <c r="G31">
-        <v>1.546733274964478E-08</v>
+        <v>1.611708134799772E-08</v>
       </c>
       <c r="H31">
-        <v>6.18148671352945E-10</v>
+        <v>9.050124887260265E-10</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2440,22 +2440,22 @@
         <v>20</v>
       </c>
       <c r="C32">
-        <v>1135.107599103973</v>
+        <v>1102.018434853326</v>
       </c>
       <c r="D32">
-        <v>1132.429878035003</v>
+        <v>1098.007616848947</v>
       </c>
       <c r="E32">
-        <v>1127.631174370112</v>
+        <v>1090.545277453129</v>
       </c>
       <c r="F32">
-        <v>1118.926703006247</v>
+        <v>1077.220637465002</v>
       </c>
       <c r="G32">
-        <v>1106.339973003008</v>
+        <v>1058.175123328153</v>
       </c>
       <c r="H32">
-        <v>1090.175315012526</v>
+        <v>1033.703153732323</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2466,22 +2466,22 @@
         <v>21</v>
       </c>
       <c r="C33">
-        <v>584.6400076402988</v>
+        <v>584.6400068104439</v>
       </c>
       <c r="D33">
-        <v>584.6400191367815</v>
+        <v>584.640019117818</v>
       </c>
       <c r="E33">
-        <v>584.6399999947339</v>
+        <v>584.6399999946422</v>
       </c>
       <c r="F33">
-        <v>906.3563707506878</v>
+        <v>906.3563707507544</v>
       </c>
       <c r="G33">
-        <v>1370.567546960825</v>
+        <v>1370.567546928048</v>
       </c>
       <c r="H33">
-        <v>1514.044699087075</v>
+        <v>1514.04469907254</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2492,22 +2492,22 @@
         <v>22</v>
       </c>
       <c r="C34">
-        <v>3787.200008519675</v>
+        <v>3787.200007594366</v>
       </c>
       <c r="D34">
-        <v>3787.200021345691</v>
+        <v>3787.200021324538</v>
       </c>
       <c r="E34">
-        <v>3787.199999992479</v>
+        <v>3787.199999992353</v>
       </c>
       <c r="F34">
-        <v>5884.933078750925</v>
+        <v>5884.933078751017</v>
       </c>
       <c r="G34">
-        <v>10176.42951944559</v>
+        <v>10077.74028317534</v>
       </c>
       <c r="H34">
-        <v>11886.37118368265</v>
+        <v>11770.66035889583</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2518,22 +2518,22 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>-6.026168145650603E-06</v>
+        <v>-6.073786120127589E-06</v>
       </c>
       <c r="D35">
-        <v>-1.438458788737826E-05</v>
+        <v>-2.81053820272676E-05</v>
       </c>
       <c r="E35">
-        <v>1.51898629708161E-08</v>
+        <v>1.424310462652971E-08</v>
       </c>
       <c r="F35">
-        <v>8.985161640506476E-09</v>
+        <v>4.213415075559838E-09</v>
       </c>
       <c r="G35">
-        <v>5.233163083494028E-08</v>
+        <v>1.09194883308975E-08</v>
       </c>
       <c r="H35">
-        <v>9.732948854874921E-09</v>
+        <v>1.02089183084598E-08</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2544,22 +2544,22 @@
         <v>13</v>
       </c>
       <c r="C36">
-        <v>11346.48571</v>
+        <v>4970.39329</v>
       </c>
       <c r="D36">
-        <v>10312.17593</v>
+        <v>4519.3539</v>
       </c>
       <c r="E36">
-        <v>9311.11802</v>
+        <v>4093.526394</v>
       </c>
       <c r="F36">
-        <v>8170.54772</v>
+        <v>3603.343382</v>
       </c>
       <c r="G36">
-        <v>7128.92508</v>
+        <v>3150.283235</v>
       </c>
       <c r="H36">
-        <v>5865.19856</v>
+        <v>2597.017379</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2596,22 +2596,22 @@
         <v>15</v>
       </c>
       <c r="C38">
-        <v>5040.543813859038</v>
+        <v>7459.591858747125</v>
       </c>
       <c r="D38">
-        <v>4573.05927671179</v>
+        <v>6770.818312844426</v>
       </c>
       <c r="E38">
-        <v>4079.25335152554</v>
+        <v>6058.773710267333</v>
       </c>
       <c r="F38">
-        <v>3536.842448069912</v>
+        <v>5269.610104913033</v>
       </c>
       <c r="G38">
-        <v>3062.361496335225</v>
+        <v>4571.832371233103</v>
       </c>
       <c r="H38">
-        <v>2500.393479924393</v>
+        <v>3740.320198960136</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2648,22 +2648,22 @@
         <v>17</v>
       </c>
       <c r="C40">
-        <v>14516.29453215309</v>
+        <v>8140.202133735163</v>
       </c>
       <c r="D40">
-        <v>13828.52385167988</v>
+        <v>8035.701807912356</v>
       </c>
       <c r="E40">
-        <v>13445.29877552367</v>
+        <v>8227.707149514094</v>
       </c>
       <c r="F40">
-        <v>10942.91627278888</v>
+        <v>6375.711934783879</v>
       </c>
       <c r="G40">
-        <v>1600.978166131761</v>
+        <v>4.597858821994212E-08</v>
       </c>
       <c r="H40">
-        <v>4.300047299609434E-08</v>
+        <v>5.388263916527091E-08</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2700,22 +2700,22 @@
         <v>19</v>
       </c>
       <c r="C42">
-        <v>-3.590530509919666E-05</v>
+        <v>-3.620328523157505E-05</v>
       </c>
       <c r="D42">
-        <v>-8.551751927474433E-05</v>
+        <v>-0.0001666050606222655</v>
       </c>
       <c r="E42">
-        <v>3.397090284934484E-09</v>
+        <v>2.803592454537809E-09</v>
       </c>
       <c r="F42">
-        <v>-1.626288069734462E-09</v>
+        <v>-5.070283234420597E-09</v>
       </c>
       <c r="G42">
-        <v>2.737771873457214E-08</v>
+        <v>7.261990511168239E-09</v>
       </c>
       <c r="H42">
-        <v>7.230798631827942E-09</v>
+        <v>1.04238543912651E-08</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2726,22 +2726,22 @@
         <v>20</v>
       </c>
       <c r="C43">
-        <v>29048.0298539987</v>
+        <v>32159.85378713937</v>
       </c>
       <c r="D43">
-        <v>26259.69066625314</v>
+        <v>29086.85202932152</v>
       </c>
       <c r="E43">
-        <v>23402.63397383807</v>
+        <v>25949.05666332908</v>
       </c>
       <c r="F43">
-        <v>20224.81798540382</v>
+        <v>22453.82202545625</v>
       </c>
       <c r="G43">
-        <v>17402.62846786705</v>
+        <v>19344.38717117685</v>
       </c>
       <c r="H43">
-        <v>14031.0797943564</v>
+        <v>15626.10129373902</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2752,22 +2752,22 @@
         <v>21</v>
       </c>
       <c r="C44">
-        <v>584.6400219163739</v>
+        <v>584.6400220973983</v>
       </c>
       <c r="D44">
-        <v>584.6400522145829</v>
+        <v>584.6401017525897</v>
       </c>
       <c r="E44">
-        <v>584.6399999937754</v>
+        <v>584.6399999942929</v>
       </c>
       <c r="F44">
-        <v>906.3563707504112</v>
+        <v>906.3563707531428</v>
       </c>
       <c r="G44">
-        <v>1370.567547885189</v>
+        <v>1370.567547367587</v>
       </c>
       <c r="H44">
-        <v>1514.044698750154</v>
+        <v>1514.044698585271</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2778,22 +2778,22 @@
         <v>22</v>
       </c>
       <c r="C45">
-        <v>3787.200024438956</v>
+        <v>3787.200024640201</v>
       </c>
       <c r="D45">
-        <v>3787.200058232358</v>
+        <v>3787.200113498285</v>
       </c>
       <c r="E45">
-        <v>3787.199999991163</v>
+        <v>3787.199999991873</v>
       </c>
       <c r="F45">
-        <v>5884.933078750547</v>
+        <v>5884.933078754291</v>
       </c>
       <c r="G45">
-        <v>15189.75288220805</v>
+        <v>12812.0892038922</v>
       </c>
       <c r="H45">
-        <v>17267.1174924243</v>
+        <v>13998.93631158688</v>
       </c>
     </row>
   </sheetData>
@@ -2840,22 +2840,22 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>-4.137268865737172E-06</v>
+        <v>-2.326277473516749E-06</v>
       </c>
       <c r="D2">
-        <v>-5.337344912889335E-06</v>
+        <v>-5.280825059172922E-06</v>
       </c>
       <c r="E2">
-        <v>1.359657478370988E-08</v>
+        <v>1.32094882299109E-08</v>
       </c>
       <c r="F2">
-        <v>8.323978783687006E-09</v>
+        <v>1.048896555166179E-08</v>
       </c>
       <c r="G2">
-        <v>1.329665962091719E-08</v>
+        <v>1.600982617003309E-08</v>
       </c>
       <c r="H2">
-        <v>1.380055163845424E-09</v>
+        <v>2.52750487088571E-09</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2866,22 +2866,22 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>1548.953883</v>
+        <v>679.146645</v>
       </c>
       <c r="D3">
-        <v>1406.133985</v>
+        <v>614.167962</v>
       </c>
       <c r="E3">
-        <v>1269.866173</v>
+        <v>557.122759</v>
       </c>
       <c r="F3">
-        <v>1114.055958</v>
+        <v>492.908485</v>
       </c>
       <c r="G3">
-        <v>971.267247</v>
+        <v>429.747239</v>
       </c>
       <c r="H3">
-        <v>799.167195</v>
+        <v>354.9008054</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2918,22 +2918,22 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>706.5252046229105</v>
+        <v>1046.552510364412</v>
       </c>
       <c r="D5">
-        <v>640.2600002369447</v>
+        <v>944.7678613550738</v>
       </c>
       <c r="E5">
-        <v>571.2286093885527</v>
+        <v>846.6641787174353</v>
       </c>
       <c r="F5">
-        <v>495.1590250938695</v>
+        <v>740.137271781346</v>
       </c>
       <c r="G5">
-        <v>428.3949051289647</v>
+        <v>640.3640423791363</v>
       </c>
       <c r="H5">
-        <v>349.8133962848315</v>
+        <v>524.8244556107649</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2970,22 +2970,22 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>4724.135195101003</v>
+        <v>3854.391388621626</v>
       </c>
       <c r="D7">
-        <v>4927.305535027705</v>
+        <v>4135.642884119951</v>
       </c>
       <c r="E7">
-        <v>5408.375334327679</v>
+        <v>4695.647740751352</v>
       </c>
       <c r="F7">
-        <v>3890.45270438711</v>
+        <v>3269.165813425382</v>
       </c>
       <c r="G7">
-        <v>6.404357818640825E-08</v>
+        <v>7.612491742112622E-08</v>
       </c>
       <c r="H7">
-        <v>1.812669770777974E-08</v>
+        <v>2.177021684625424E-08</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3022,22 +3022,22 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>-2.467400292538719E-05</v>
+        <v>-1.388403748349822E-05</v>
       </c>
       <c r="D9">
-        <v>-3.16705718905404E-05</v>
+        <v>-3.133587717102144E-05</v>
       </c>
       <c r="E9">
-        <v>2.405792839158795E-09</v>
+        <v>2.153877732163145E-09</v>
       </c>
       <c r="F9">
-        <v>-3.252274243045185E-09</v>
+        <v>-1.875233724626027E-09</v>
       </c>
       <c r="G9">
-        <v>1.256583993845725E-08</v>
+        <v>1.603122814138357E-08</v>
       </c>
       <c r="H9">
-        <v>-1.546610445331474E-10</v>
+        <v>9.317297624345305E-10</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3048,22 +3048,22 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <v>17415.5978922647</v>
+        <v>17850.76034274715</v>
       </c>
       <c r="D10">
-        <v>15686.93082833882</v>
+        <v>16008.11232577732</v>
       </c>
       <c r="E10">
-        <v>13951.9659195027</v>
+        <v>14261.48980339886</v>
       </c>
       <c r="F10">
-        <v>12010.37809895438</v>
+        <v>12352.94796878072</v>
       </c>
       <c r="G10">
-        <v>10274.51945846324</v>
+        <v>10549.52056902634</v>
       </c>
       <c r="H10">
-        <v>8210.160261668256</v>
+        <v>8452.141847454875</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3074,22 +3074,22 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>584.6400150593709</v>
+        <v>584.6400084731434</v>
       </c>
       <c r="D11">
-        <v>584.6400193404887</v>
+        <v>584.640019136056</v>
       </c>
       <c r="E11">
-        <v>584.6399999946397</v>
+        <v>584.6399999948594</v>
       </c>
       <c r="F11">
-        <v>906.3563707517009</v>
+        <v>906.3563707506087</v>
       </c>
       <c r="G11">
-        <v>1370.567547107193</v>
+        <v>1370.567546932378</v>
       </c>
       <c r="H11">
-        <v>1514.044699126232</v>
+        <v>1514.044699071186</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3100,22 +3100,22 @@
         <v>22</v>
       </c>
       <c r="C12">
-        <v>3787.200016792189</v>
+        <v>3787.200009448313</v>
       </c>
       <c r="D12">
-        <v>3787.200021572925</v>
+        <v>3787.200021344882</v>
       </c>
       <c r="E12">
-        <v>3787.19999999235</v>
+        <v>3787.199999992652</v>
       </c>
       <c r="F12">
-        <v>5884.933078752314</v>
+        <v>5884.933078750817</v>
       </c>
       <c r="G12">
-        <v>10636.39352984886</v>
+        <v>10094.94233133003</v>
       </c>
       <c r="H12">
-        <v>12203.87222689544</v>
+        <v>11759.58360323902</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3126,22 +3126,22 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>-8.651981600322581E-06</v>
+        <v>-6.258881342522619E-06</v>
       </c>
       <c r="D13">
-        <v>-2.042724016336509E-05</v>
+        <v>-1.652840861421949E-05</v>
       </c>
       <c r="E13">
-        <v>5.632056022764167E-09</v>
+        <v>5.424686177451491E-09</v>
       </c>
       <c r="F13">
-        <v>2.921208439933238E-08</v>
+        <v>2.863344272584747E-08</v>
       </c>
       <c r="G13">
-        <v>2.711272901101618E-08</v>
+        <v>1.439358689917164E-08</v>
       </c>
       <c r="H13">
-        <v>1.673503569368618E-08</v>
+        <v>1.581866941409898E-08</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3152,22 +3152,22 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>4250.22071</v>
+        <v>1864.31004</v>
       </c>
       <c r="D14">
-        <v>3861.760608</v>
+        <v>1691.605019</v>
       </c>
       <c r="E14">
-        <v>3493.213732</v>
+        <v>1537.070918</v>
       </c>
       <c r="F14">
-        <v>3074.458159</v>
+        <v>1357.581588</v>
       </c>
       <c r="G14">
-        <v>2670.384416</v>
+        <v>1180.336566</v>
       </c>
       <c r="H14">
-        <v>2194.775716</v>
+        <v>974.0417189999999</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3204,22 +3204,22 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>1938.655555864752</v>
+        <v>2872.867520470197</v>
       </c>
       <c r="D16">
-        <v>1758.389220939063</v>
+        <v>2602.17751517763</v>
       </c>
       <c r="E16">
-        <v>1571.365279479722</v>
+        <v>2335.899703393814</v>
       </c>
       <c r="F16">
-        <v>1366.489439449663</v>
+        <v>2038.505646958023</v>
       </c>
       <c r="G16">
-        <v>1177.821116925065</v>
+        <v>1758.81315245721</v>
       </c>
       <c r="H16">
-        <v>960.7025315242845</v>
+        <v>1440.405051097002</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3256,22 +3256,22 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>9014.610069462642</v>
+        <v>6628.153909858675</v>
       </c>
       <c r="D18">
-        <v>8960.154220705577</v>
+        <v>6790.180711588533</v>
       </c>
       <c r="E18">
-        <v>9195.988557353452</v>
+        <v>7239.558313155341</v>
       </c>
       <c r="F18">
-        <v>8206.773292410722</v>
+        <v>6489.530806604364</v>
       </c>
       <c r="G18">
-        <v>2327.054567740735</v>
+        <v>1249.9620403346</v>
       </c>
       <c r="H18">
-        <v>977.4054221763303</v>
+        <v>252.7844871432927</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3308,22 +3308,22 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>-4.840058605678994E-05</v>
+        <v>-3.50310617425377E-05</v>
       </c>
       <c r="D20">
-        <v>-0.0001141096241852854</v>
+        <v>-9.217074909269748E-05</v>
       </c>
       <c r="E20">
-        <v>-2.247783390814225E-09</v>
+        <v>-2.38192609513623E-09</v>
       </c>
       <c r="F20">
-        <v>1.155564924376144E-08</v>
+        <v>1.120737974608264E-08</v>
       </c>
       <c r="G20">
-        <v>8.973394806927529E-09</v>
+        <v>3.645769606947673E-09</v>
       </c>
       <c r="H20">
-        <v>7.481117629968873E-09</v>
+        <v>6.977536726247324E-09</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3334,22 +3334,22 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>18293.74116925076</v>
+        <v>19467.69882628137</v>
       </c>
       <c r="D21">
-        <v>16497.91217532455</v>
+        <v>17530.17602890515</v>
       </c>
       <c r="E21">
-        <v>14698.49940523827</v>
+        <v>15652.62347222194</v>
       </c>
       <c r="F21">
-        <v>12699.54174810095</v>
+        <v>13542.91643001087</v>
       </c>
       <c r="G21">
-        <v>10824.61844544382</v>
+        <v>11543.18173649665</v>
       </c>
       <c r="H21">
-        <v>8647.364518492239</v>
+        <v>9258.292206063767</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3360,22 +3360,22 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>389.7600293646336</v>
+        <v>389.7600212521202</v>
       </c>
       <c r="D22">
-        <v>389.7600692430594</v>
+        <v>389.7600559408655</v>
       </c>
       <c r="E22">
-        <v>389.7599999986971</v>
+        <v>389.759999998814</v>
       </c>
       <c r="F22">
-        <v>604.2375804894766</v>
+        <v>604.2375804897528</v>
       </c>
       <c r="G22">
-        <v>913.7116987135133</v>
+        <v>913.7116984833403</v>
       </c>
       <c r="H22">
-        <v>1009.363132505755</v>
+        <v>1009.363132582759</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3386,22 +3386,22 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>2524.800034940915</v>
+        <v>2524.800025287544</v>
       </c>
       <c r="D23">
-        <v>2524.800082396614</v>
+        <v>2524.80006657305</v>
       </c>
       <c r="E23">
-        <v>2524.799999997922</v>
+        <v>2524.799999998083</v>
       </c>
       <c r="F23">
-        <v>3923.288719152138</v>
+        <v>3923.288719152517</v>
       </c>
       <c r="G23">
-        <v>10546.72049057759</v>
+        <v>10133.70308689862</v>
       </c>
       <c r="H23">
-        <v>13193.61025743599</v>
+        <v>12697.02191505176</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3412,22 +3412,22 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>-2.323951066010193E-06</v>
+        <v>-2.097432213695274E-06</v>
       </c>
       <c r="D24">
-        <v>-5.291702908067196E-06</v>
+        <v>-5.280510469549603E-06</v>
       </c>
       <c r="E24">
-        <v>1.345996520927016E-08</v>
+        <v>1.32207561099039E-08</v>
       </c>
       <c r="F24">
-        <v>9.794149554209167E-09</v>
+        <v>1.03749380780764E-08</v>
       </c>
       <c r="G24">
-        <v>1.451363776669799E-08</v>
+        <v>1.561354181911984E-08</v>
       </c>
       <c r="H24">
-        <v>1.573471809548865E-09</v>
+        <v>2.225607975230055E-09</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3438,22 +3438,22 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <v>260.0596921</v>
+        <v>113.9206433</v>
       </c>
       <c r="D25">
-        <v>270.6325297</v>
+        <v>118.6058293</v>
       </c>
       <c r="E25">
-        <v>292.2947515</v>
+        <v>128.5040403</v>
       </c>
       <c r="F25">
-        <v>329.518968</v>
+        <v>145.3231818</v>
       </c>
       <c r="G25">
-        <v>381.153474</v>
+        <v>168.4323221</v>
       </c>
       <c r="H25">
-        <v>447.601435</v>
+        <v>198.1908527</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3490,22 +3490,22 @@
         <v>15</v>
       </c>
       <c r="C27">
-        <v>118.6211734732545</v>
+        <v>175.5496186138564</v>
       </c>
       <c r="D27">
-        <v>123.2280731117614</v>
+        <v>182.4500516517178</v>
       </c>
       <c r="E27">
-        <v>131.4840323014809</v>
+        <v>195.2886785705722</v>
       </c>
       <c r="F27">
-        <v>146.4596891761186</v>
+        <v>218.2131289309004</v>
       </c>
       <c r="G27">
-        <v>168.1146020338258</v>
+        <v>250.9800953510163</v>
       </c>
       <c r="H27">
-        <v>195.9251804291587</v>
+        <v>293.0830364241463</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3542,22 +3542,22 @@
         <v>17</v>
       </c>
       <c r="C29">
-        <v>3977.252389211375</v>
+        <v>3831.113331955036</v>
       </c>
       <c r="D29">
-        <v>4283.997857516304</v>
+        <v>4131.971157543178</v>
       </c>
       <c r="E29">
-        <v>4872.323417117317</v>
+        <v>4708.532705919803</v>
       </c>
       <c r="F29">
-        <v>3490.618780728733</v>
+        <v>3306.422994528419</v>
       </c>
       <c r="G29">
-        <v>6.945212772644136E-08</v>
+        <v>7.435208007290321E-08</v>
       </c>
       <c r="H29">
-        <v>1.874271125993457E-08</v>
+        <v>2.07992492619647E-08</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3594,22 +3594,22 @@
         <v>19</v>
       </c>
       <c r="C31">
-        <v>-1.386987131687674E-05</v>
+        <v>-1.252027974473163E-05</v>
       </c>
       <c r="D31">
-        <v>-3.140029328181524E-05</v>
+        <v>-3.133401408971914E-05</v>
       </c>
       <c r="E31">
-        <v>2.322358689795786E-09</v>
+        <v>2.160709456877551E-09</v>
       </c>
       <c r="F31">
-        <v>-2.383914435047194E-09</v>
+        <v>-1.959272277368847E-09</v>
       </c>
       <c r="G31">
-        <v>1.41172179279471E-08</v>
+        <v>1.55227108726971E-08</v>
       </c>
       <c r="H31">
-        <v>2.901617372853832E-11</v>
+        <v>6.422156368327874E-10</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3620,22 +3620,22 @@
         <v>20</v>
       </c>
       <c r="C32">
-        <v>1007.29029117528</v>
+        <v>937.1349749120725</v>
       </c>
       <c r="D32">
-        <v>1001.613015073077</v>
+        <v>928.6312811799039</v>
       </c>
       <c r="E32">
-        <v>991.4388494765917</v>
+        <v>912.8097014818635</v>
       </c>
       <c r="F32">
-        <v>972.9837179216256</v>
+        <v>884.5589375409742</v>
       </c>
       <c r="G32">
-        <v>946.2974584175677</v>
+        <v>844.1788272725207</v>
       </c>
       <c r="H32">
-        <v>912.0253134824904</v>
+        <v>792.2936029474677</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3646,22 +3646,22 @@
         <v>21</v>
       </c>
       <c r="C33">
-        <v>584.6400084645148</v>
+        <v>584.640007640719</v>
       </c>
       <c r="D33">
-        <v>584.6400191754017</v>
+        <v>584.6400191349181</v>
       </c>
       <c r="E33">
-        <v>584.6399999947124</v>
+        <v>584.6399999948534</v>
       </c>
       <c r="F33">
-        <v>906.3563707510122</v>
+        <v>906.3563707506753</v>
       </c>
       <c r="G33">
-        <v>1370.567547028932</v>
+        <v>1370.567546958031</v>
       </c>
       <c r="H33">
-        <v>1514.044699116925</v>
+        <v>1514.044699085855</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3672,22 +3672,22 @@
         <v>22</v>
       </c>
       <c r="C34">
-        <v>3787.200009438705</v>
+        <v>3787.200008520143</v>
       </c>
       <c r="D34">
-        <v>3787.200021388772</v>
+        <v>3787.200021343613</v>
       </c>
       <c r="E34">
-        <v>3787.19999999245</v>
+        <v>3787.199999992643</v>
       </c>
       <c r="F34">
-        <v>5884.93307875137</v>
+        <v>5884.933078750909</v>
       </c>
       <c r="G34">
-        <v>10380.75175288775</v>
+        <v>10168.03060105029</v>
       </c>
       <c r="H34">
-        <v>12126.31370315672</v>
+        <v>11876.90312088357</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3698,22 +3698,22 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>-6.026168145650603E-06</v>
+        <v>-6.073786120127589E-06</v>
       </c>
       <c r="D35">
-        <v>-1.438458788737826E-05</v>
+        <v>-2.81053820272676E-05</v>
       </c>
       <c r="E35">
-        <v>1.51898629708161E-08</v>
+        <v>1.424310462652971E-08</v>
       </c>
       <c r="F35">
-        <v>8.985161640506476E-09</v>
+        <v>4.213415075559838E-09</v>
       </c>
       <c r="G35">
-        <v>5.233163083494028E-08</v>
+        <v>1.09194883308975E-08</v>
       </c>
       <c r="H35">
-        <v>9.732948854874921E-09</v>
+        <v>1.02089183084598E-08</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3724,22 +3724,22 @@
         <v>13</v>
       </c>
       <c r="C36">
-        <v>11346.48571</v>
+        <v>4970.39329</v>
       </c>
       <c r="D36">
-        <v>10312.17593</v>
+        <v>4519.3539</v>
       </c>
       <c r="E36">
-        <v>9311.11802</v>
+        <v>4093.526394</v>
       </c>
       <c r="F36">
-        <v>8170.54772</v>
+        <v>3603.343382</v>
       </c>
       <c r="G36">
-        <v>7128.92508</v>
+        <v>3150.283235</v>
       </c>
       <c r="H36">
-        <v>5865.19856</v>
+        <v>2597.017379</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -3776,22 +3776,22 @@
         <v>15</v>
       </c>
       <c r="C38">
-        <v>5175.478903793681</v>
+        <v>7659.284736243443</v>
       </c>
       <c r="D38">
-        <v>4695.479830439133</v>
+        <v>6952.072759133094</v>
       </c>
       <c r="E38">
-        <v>4188.454746887061</v>
+        <v>6220.966760398301</v>
       </c>
       <c r="F38">
-        <v>3631.523532381249</v>
+        <v>5410.677287281706</v>
       </c>
       <c r="G38">
-        <v>3144.340750792696</v>
+        <v>4694.220080766007</v>
       </c>
       <c r="H38">
-        <v>2567.328880457552</v>
+        <v>3840.448371845643</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3828,22 +3828,22 @@
         <v>17</v>
       </c>
       <c r="C40">
-        <v>14516.29453215309</v>
+        <v>8140.202133735163</v>
       </c>
       <c r="D40">
-        <v>13828.52385167988</v>
+        <v>8035.701807912356</v>
       </c>
       <c r="E40">
-        <v>13445.29877552367</v>
+        <v>8227.707149514094</v>
       </c>
       <c r="F40">
-        <v>10942.91627278888</v>
+        <v>6375.711934783879</v>
       </c>
       <c r="G40">
-        <v>1600.978166131761</v>
+        <v>4.597858821994212E-08</v>
       </c>
       <c r="H40">
-        <v>4.300047299609434E-08</v>
+        <v>5.388263916527091E-08</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -3880,22 +3880,22 @@
         <v>19</v>
       </c>
       <c r="C42">
-        <v>-3.590530509919666E-05</v>
+        <v>-3.620328523157505E-05</v>
       </c>
       <c r="D42">
-        <v>-8.551751927474433E-05</v>
+        <v>-0.0001666050606222655</v>
       </c>
       <c r="E42">
-        <v>3.397090284934484E-09</v>
+        <v>2.803592454537809E-09</v>
       </c>
       <c r="F42">
-        <v>-1.626288069734462E-09</v>
+        <v>-5.070283234420597E-09</v>
       </c>
       <c r="G42">
-        <v>2.737771873457214E-08</v>
+        <v>7.261990511168239E-09</v>
       </c>
       <c r="H42">
-        <v>7.230798631827942E-09</v>
+        <v>1.04238543912651E-08</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -3906,22 +3906,22 @@
         <v>20</v>
       </c>
       <c r="C43">
-        <v>27993.86904886855</v>
+        <v>31054.7673973399</v>
       </c>
       <c r="D43">
-        <v>25307.2586742386</v>
+        <v>28088.15300920318</v>
       </c>
       <c r="E43">
-        <v>22553.9494995051</v>
+        <v>25058.69950215274</v>
       </c>
       <c r="F43">
-        <v>19491.75417726302</v>
+        <v>21684.28014644487</v>
       </c>
       <c r="G43">
-        <v>16772.48486275269</v>
+        <v>18682.46631922033</v>
       </c>
       <c r="H43">
-        <v>13524.05136296709</v>
+        <v>15092.97003514568</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -3932,22 +3932,22 @@
         <v>21</v>
       </c>
       <c r="C44">
-        <v>584.6400219163739</v>
+        <v>584.6400220973983</v>
       </c>
       <c r="D44">
-        <v>584.6400522145829</v>
+        <v>584.6401017525897</v>
       </c>
       <c r="E44">
-        <v>584.6399999937754</v>
+        <v>584.6399999942929</v>
       </c>
       <c r="F44">
-        <v>906.3563707504112</v>
+        <v>906.3563707531428</v>
       </c>
       <c r="G44">
-        <v>1370.567547885189</v>
+        <v>1370.567547367587</v>
       </c>
       <c r="H44">
-        <v>1514.044698750154</v>
+        <v>1514.044698585271</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -3958,22 +3958,22 @@
         <v>22</v>
       </c>
       <c r="C45">
-        <v>3787.200024438956</v>
+        <v>3787.200024640201</v>
       </c>
       <c r="D45">
-        <v>3787.200058232358</v>
+        <v>3787.200113498285</v>
       </c>
       <c r="E45">
-        <v>3787.199999991163</v>
+        <v>3787.199999991873</v>
       </c>
       <c r="F45">
-        <v>5884.933078750547</v>
+        <v>5884.933078754291</v>
       </c>
       <c r="G45">
-        <v>15189.75288220805</v>
+        <v>12812.0892038922</v>
       </c>
       <c r="H45">
-        <v>17267.1174924243</v>
+        <v>13998.93631158688</v>
       </c>
     </row>
   </sheetData>
@@ -4020,22 +4020,22 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>-3.290834883806798E-06</v>
+        <v>4309.51587324581</v>
       </c>
       <c r="D2">
-        <v>-7.490350817240465E-06</v>
+        <v>3916.705960024969</v>
       </c>
       <c r="E2">
-        <v>5.375446085865391E-08</v>
+        <v>3479.852949520258</v>
       </c>
       <c r="F2">
-        <v>1.515004007041895E-08</v>
+        <v>3018.705435292744</v>
       </c>
       <c r="G2">
-        <v>4.477543097542076E-09</v>
+        <v>2592.548681794009</v>
       </c>
       <c r="H2">
-        <v>9.32288355388299E-09</v>
+        <v>2121.326619410986</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4046,22 +4046,22 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>9654.82762</v>
+        <v>4254.25786</v>
       </c>
       <c r="D3">
-        <v>8805.479219999999</v>
+        <v>3876.669098</v>
       </c>
       <c r="E3">
-        <v>7977.195009999999</v>
+        <v>3050.191076</v>
       </c>
       <c r="F3">
-        <v>6961.20032</v>
+        <v>3097.524741</v>
       </c>
       <c r="G3">
-        <v>6081.97529</v>
+        <v>2690.576411</v>
       </c>
       <c r="H3">
-        <v>5014.03829</v>
+        <v>2226.335311</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4072,22 +4072,22 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>3357.122248005902</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3059.732060391121</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2771.471368592259</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2449.419396498193</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2128.356772702386</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1761.528332747125</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4098,22 +4098,22 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>11305.00231</v>
+        <v>16828.99695</v>
       </c>
       <c r="D5">
-        <v>10292.47032</v>
+        <v>15308.53548</v>
       </c>
       <c r="E5">
-        <v>9211.68686</v>
+        <v>11899.37894</v>
       </c>
       <c r="F5">
-        <v>7942.528520000001</v>
+        <v>11939.81855</v>
       </c>
       <c r="G5">
-        <v>6886.31938</v>
+        <v>10291.91363</v>
       </c>
       <c r="H5">
-        <v>5634.084980000001</v>
+        <v>8451.51583</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4150,22 +4150,22 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>8458.071241614098</v>
+        <v>8.358558590707425E-09</v>
       </c>
       <c r="D7">
-        <v>7954.908599957565</v>
+        <v>1.392351208466343E-08</v>
       </c>
       <c r="E7">
-        <v>7744.055876580582</v>
+        <v>1.558662263468618E-08</v>
       </c>
       <c r="F7">
-        <v>3092.420523036476</v>
+        <v>6.145958041756861E-09</v>
       </c>
       <c r="G7">
-        <v>1.318160529529138E-08</v>
+        <v>2.007392514828445E-09</v>
       </c>
       <c r="H7">
-        <v>2.554048977707335E-08</v>
+        <v>2.671205011525862E-08</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4202,22 +4202,22 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>-2.488631242033806E-05</v>
+        <v>-3.955828441606989E-09</v>
       </c>
       <c r="D9">
-        <v>-5.619005889669898E-05</v>
+        <v>-5.263892420676037E-10</v>
       </c>
       <c r="E9">
-        <v>2.647377230678711E-08</v>
+        <v>-2.427262503519055E-09</v>
       </c>
       <c r="F9">
-        <v>2.646674294876444E-09</v>
+        <v>-4.358983789998543E-09</v>
       </c>
       <c r="G9">
-        <v>-2.023310947427042E-09</v>
+        <v>-5.22850074208452E-09</v>
       </c>
       <c r="H9">
-        <v>1.870685655914833E-09</v>
+        <v>1.818569637510487E-09</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4254,22 +4254,22 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>1169.280015491007</v>
+        <v>1169.279999609148</v>
       </c>
       <c r="D11">
-        <v>1169.280034998013</v>
+        <v>1169.279999437794</v>
       </c>
       <c r="E11">
-        <v>1169.279999973655</v>
+        <v>1169.279999529733</v>
       </c>
       <c r="F11">
-        <v>1812.712741306197</v>
+        <v>1812.712741126323</v>
       </c>
       <c r="G11">
-        <v>2741.135096182392</v>
+        <v>2741.135096344081</v>
       </c>
       <c r="H11">
-        <v>3028.08939873201</v>
+        <v>3028.089398711199</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4280,22 +4280,22 @@
         <v>22</v>
       </c>
       <c r="C12">
-        <v>7574.400013587989</v>
+        <v>2965.426593718425</v>
       </c>
       <c r="D12">
-        <v>7574.400030722712</v>
+        <v>3624.062537331216</v>
       </c>
       <c r="E12">
-        <v>7574.39999996353</v>
+        <v>4140.048723717395</v>
       </c>
       <c r="F12">
-        <v>11623.47778785415</v>
+        <v>5384.237977294659</v>
       </c>
       <c r="G12">
-        <v>14376.45782250095</v>
+        <v>6264.338151893873</v>
       </c>
       <c r="H12">
-        <v>14904.68560890527</v>
+        <v>8234.147878453427</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4306,22 +4306,22 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>-4.697071390639983E-06</v>
+        <v>-4.735771891767304E-06</v>
       </c>
       <c r="D13">
-        <v>-1.548157707396548E-05</v>
+        <v>-1.246167243276618E-05</v>
       </c>
       <c r="E13">
-        <v>2.27810171706588E-08</v>
+        <v>1.96315791071028E-08</v>
       </c>
       <c r="F13">
-        <v>1.190433117111625E-08</v>
+        <v>1.209574108505396E-08</v>
       </c>
       <c r="G13">
-        <v>9.173821701728333E-10</v>
+        <v>1.271528019379904E-09</v>
       </c>
       <c r="H13">
-        <v>1.563618722447096E-08</v>
+        <v>4.981224440253174E-09</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4332,22 +4332,22 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>4256.17062</v>
+        <v>1853.675816</v>
       </c>
       <c r="D14">
-        <v>3867.194314</v>
+        <v>1700.054915</v>
       </c>
       <c r="E14">
-        <v>3479.563475</v>
+        <v>1533.693409</v>
       </c>
       <c r="F14">
-        <v>3059.21069</v>
+        <v>1352.669537</v>
       </c>
       <c r="G14">
-        <v>2666.554334</v>
+        <v>1180.512491</v>
       </c>
       <c r="H14">
-        <v>2196.716799</v>
+        <v>973.597699</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4384,22 +4384,22 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>4983.62276</v>
+        <v>7332.77238</v>
       </c>
       <c r="D16">
-        <v>4520.25174</v>
+        <v>6713.328</v>
       </c>
       <c r="E16">
-        <v>4018.035053</v>
+        <v>5983.23135</v>
       </c>
       <c r="F16">
-        <v>3490.471037</v>
+        <v>5214.04349</v>
       </c>
       <c r="G16">
-        <v>3019.207412</v>
+        <v>4515.6616</v>
       </c>
       <c r="H16">
-        <v>2468.367505</v>
+        <v>3695.928615</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4436,22 +4436,22 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>6105.42602127292</v>
+        <v>3705.302123116567</v>
       </c>
       <c r="D18">
-        <v>6050.50428946252</v>
+        <v>3882.212149891448</v>
       </c>
       <c r="E18">
-        <v>6269.085540203124</v>
+        <v>4322.356529321232</v>
       </c>
       <c r="F18">
-        <v>3665.450384829453</v>
+        <v>2043.389469796306</v>
       </c>
       <c r="G18">
-        <v>2.037192899317211E-08</v>
+        <v>1.885101269359012E-08</v>
       </c>
       <c r="H18">
-        <v>4.974686614714887E-08</v>
+        <v>1.094607473650725E-08</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4488,22 +4488,22 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>-3.004435756359065E-05</v>
+        <v>-3.029535592814502E-05</v>
       </c>
       <c r="D20">
-        <v>-9.832985389998495E-05</v>
+        <v>-7.915650638695071E-05</v>
       </c>
       <c r="E20">
-        <v>7.950503115635591E-09</v>
+        <v>5.199506830844289E-09</v>
       </c>
       <c r="F20">
-        <v>-9.431092762667831E-10</v>
+        <v>-2.18730140923961E-10</v>
       </c>
       <c r="G20">
-        <v>-4.720902682990214E-11</v>
+        <v>-3.971089883100637E-10</v>
       </c>
       <c r="H20">
-        <v>8.684056558730494E-09</v>
+        <v>-2.295712727828538E-09</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4540,22 +4540,22 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>779.5200184533276</v>
+        <v>779.5200186073039</v>
       </c>
       <c r="D22">
-        <v>779.5200604368003</v>
+        <v>779.5200486517676</v>
       </c>
       <c r="E22">
-        <v>779.5199999898052</v>
+        <v>779.5199999922038</v>
       </c>
       <c r="F22">
-        <v>1208.475161000349</v>
+        <v>1208.475160944642</v>
       </c>
       <c r="G22">
-        <v>1827.423397184865</v>
+        <v>1827.423397207532</v>
       </c>
       <c r="H22">
-        <v>2018.726265216427</v>
+        <v>2018.726265807789</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4566,22 +4566,22 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>5049.600019155382</v>
+        <v>5049.600019315026</v>
       </c>
       <c r="D23">
-        <v>5049.600062769136</v>
+        <v>5049.600050529323</v>
       </c>
       <c r="E23">
-        <v>5049.59999998571</v>
+        <v>5049.599999989005</v>
       </c>
       <c r="F23">
-        <v>7846.577438333878</v>
+        <v>7761.340255539808</v>
       </c>
       <c r="G23">
-        <v>11956.59624190194</v>
+        <v>10470.09162661469</v>
       </c>
       <c r="H23">
-        <v>13163.41041871412</v>
+        <v>11940.09389681301</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -4592,22 +4592,22 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>-2.980763105589842E-06</v>
+        <v>-2.051611052306004E-06</v>
       </c>
       <c r="D24">
-        <v>-4.496459926356693E-06</v>
+        <v>-7.408291566541459E-07</v>
       </c>
       <c r="E24">
-        <v>3.566991665068605E-08</v>
+        <v>6.489567141248733E-09</v>
       </c>
       <c r="F24">
-        <v>1.090503071845331E-08</v>
+        <v>4.571649773973632E-09</v>
       </c>
       <c r="G24">
-        <v>4.850061357586051E-09</v>
+        <v>4.82757797840384E-09</v>
       </c>
       <c r="H24">
-        <v>1.198244058803694E-08</v>
+        <v>1.499658982055828E-08</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4618,22 +4618,22 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <v>3438.65402</v>
+        <v>1506.322148</v>
       </c>
       <c r="D25">
-        <v>3578.45388</v>
+        <v>1568.272292</v>
       </c>
       <c r="E25">
-        <v>3864.88387</v>
+        <v>1699.151939</v>
       </c>
       <c r="F25">
-        <v>4357.08318</v>
+        <v>1921.543991</v>
       </c>
       <c r="G25">
-        <v>5039.82336</v>
+        <v>2227.105912</v>
       </c>
       <c r="H25">
-        <v>5918.43531</v>
+        <v>2620.589747</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4644,22 +4644,22 @@
         <v>14</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>3.52044696E-11</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>3.52044696E-11</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>3.52044696E-11</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>3.52044696E-11</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>3.52044696E-11</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>3.52044696E-11</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4670,22 +4670,22 @@
         <v>15</v>
       </c>
       <c r="C27">
-        <v>4026.37862</v>
+        <v>5958.71047</v>
       </c>
       <c r="D27">
-        <v>4182.75143</v>
+        <v>6192.93302</v>
       </c>
       <c r="E27">
-        <v>4462.98479</v>
+        <v>6628.716729999999</v>
       </c>
       <c r="F27">
-        <v>4971.30609</v>
+        <v>7406.84526</v>
       </c>
       <c r="G27">
-        <v>5706.34245</v>
+        <v>8519.059929999999</v>
       </c>
       <c r="H27">
-        <v>6650.32165</v>
+        <v>9948.16721</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4722,22 +4722,22 @@
         <v>17</v>
       </c>
       <c r="C29">
-        <v>2784.006981443362</v>
+        <v>1185.932406237588</v>
       </c>
       <c r="D29">
-        <v>3219.979268508532</v>
+        <v>1445.439917965968</v>
       </c>
       <c r="E29">
-        <v>4073.072535596453</v>
+        <v>1987.485346767303</v>
       </c>
       <c r="F29">
-        <v>1459.26420785992</v>
+        <v>56.47024737781724</v>
       </c>
       <c r="G29">
-        <v>1.554762046367707E-08</v>
+        <v>1.872088817732202E-08</v>
       </c>
       <c r="H29">
-        <v>3.422556389320612E-08</v>
+        <v>4.833638576104293E-08</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4774,22 +4774,22 @@
         <v>19</v>
       </c>
       <c r="C31">
-        <v>-2.255784822706512E-05</v>
+        <v>-1.552150224173912E-05</v>
       </c>
       <c r="D31">
-        <v>-3.386411240241864E-05</v>
+        <v>-5.657587711533438E-06</v>
       </c>
       <c r="E31">
-        <v>1.478669599646199E-08</v>
+        <v>-3.152339022539638E-09</v>
       </c>
       <c r="F31">
-        <v>1.205443576463846E-09</v>
+        <v>-1.911051535291256E-09</v>
       </c>
       <c r="G31">
-        <v>-1.344647687835329E-09</v>
+        <v>-4.344336543273871E-10</v>
       </c>
       <c r="H31">
-        <v>4.279887601048228E-09</v>
+        <v>8.427010276218382E-09</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4826,22 +4826,22 @@
         <v>21</v>
       </c>
       <c r="C33">
-        <v>1169.280014040831</v>
+        <v>1169.280009488041</v>
       </c>
       <c r="D33">
-        <v>1169.280021086668</v>
+        <v>1169.280003349994</v>
       </c>
       <c r="E33">
-        <v>1169.279999983845</v>
+        <v>1169.279999832259</v>
       </c>
       <c r="F33">
-        <v>1812.712741169096</v>
+        <v>1812.7127411033</v>
       </c>
       <c r="G33">
-        <v>2741.135096148157</v>
+        <v>2741.13509610224</v>
       </c>
       <c r="H33">
-        <v>3028.08939859942</v>
+        <v>3028.089398385743</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -4852,22 +4852,22 @@
         <v>22</v>
       </c>
       <c r="C34">
-        <v>7574.400012315234</v>
+        <v>7240.142603259998</v>
       </c>
       <c r="D34">
-        <v>7574.400018504247</v>
+        <v>7338.757718231289</v>
       </c>
       <c r="E34">
-        <v>7574.399999977524</v>
+        <v>7494.255258020832</v>
       </c>
       <c r="F34">
-        <v>11037.49549319699</v>
+        <v>10004.75026475536</v>
       </c>
       <c r="G34">
-        <v>13668.85408983903</v>
+        <v>10856.13664187794</v>
       </c>
       <c r="H34">
-        <v>16083.10287867184</v>
+        <v>12785.25731587597</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4878,22 +4878,22 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>-3.288996553410253E-06</v>
+        <v>-3.276595559628147E-06</v>
       </c>
       <c r="D35">
-        <v>-6.874735616996179E-06</v>
+        <v>-3.887074439032332E-06</v>
       </c>
       <c r="E35">
-        <v>5.580606231693413E-08</v>
+        <v>3.569583050841714E-08</v>
       </c>
       <c r="F35">
-        <v>1.260513877957031E-08</v>
+        <v>1.179113925964509E-08</v>
       </c>
       <c r="G35">
-        <v>4.21101534524156E-09</v>
+        <v>6.294805271764324E-09</v>
       </c>
       <c r="H35">
-        <v>7.410867605246439E-09</v>
+        <v>1.636291766995027E-08</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -4904,22 +4904,22 @@
         <v>13</v>
       </c>
       <c r="C36">
-        <v>11346.48571</v>
+        <v>4970.39329</v>
       </c>
       <c r="D36">
-        <v>10312.17593</v>
+        <v>4519.3539</v>
       </c>
       <c r="E36">
-        <v>9311.11802</v>
+        <v>4093.526394</v>
       </c>
       <c r="F36">
-        <v>8170.54772</v>
+        <v>3603.343382</v>
       </c>
       <c r="G36">
-        <v>7128.92508</v>
+        <v>3150.283235</v>
       </c>
       <c r="H36">
-        <v>5865.19856</v>
+        <v>2597.017379</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -4956,22 +4956,22 @@
         <v>15</v>
       </c>
       <c r="C38">
-        <v>13285.79365</v>
+        <v>19661.88606</v>
       </c>
       <c r="D38">
-        <v>12053.60456</v>
+        <v>17846.42655</v>
       </c>
       <c r="E38">
-        <v>10752.03793</v>
+        <v>15969.62952</v>
       </c>
       <c r="F38">
-        <v>9322.358990000001</v>
+        <v>13889.56332</v>
       </c>
       <c r="G38">
-        <v>8071.72885</v>
+        <v>12050.3707</v>
       </c>
       <c r="H38">
-        <v>6590.50155</v>
+        <v>9858.68275</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -5008,22 +5008,22 @@
         <v>17</v>
       </c>
       <c r="C40">
-        <v>10144.45470535275</v>
+        <v>3768.362298956158</v>
       </c>
       <c r="D40">
-        <v>9456.683972239414</v>
+        <v>3663.861934588744</v>
       </c>
       <c r="E40">
-        <v>9073.458775484725</v>
+        <v>3855.867149485256</v>
       </c>
       <c r="F40">
-        <v>4196.804181670381</v>
+        <v>620.0984267384661</v>
       </c>
       <c r="G40">
-        <v>1.109906865846262E-08</v>
+        <v>2.33648775873744E-08</v>
       </c>
       <c r="H40">
-        <v>1.744036028605798E-08</v>
+        <v>5.071069230524911E-08</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5060,22 +5060,22 @@
         <v>19</v>
       </c>
       <c r="C42">
-        <v>-2.487285203382896E-05</v>
+        <v>-2.478793362728443E-05</v>
       </c>
       <c r="D42">
-        <v>-5.154660511631935E-05</v>
+        <v>-2.928360186378148E-05</v>
       </c>
       <c r="E42">
-        <v>2.802379627097764E-08</v>
+        <v>1.46218016627421E-08</v>
       </c>
       <c r="F42">
-        <v>2.600662007712507E-10</v>
+        <v>2.38344886228367E-09</v>
       </c>
       <c r="G42">
-        <v>-2.620661768023849E-09</v>
+        <v>8.976393742404025E-10</v>
       </c>
       <c r="H42">
-        <v>-4.82461690471953E-10</v>
+        <v>9.162046354776498E-09</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -5112,22 +5112,22 @@
         <v>21</v>
       </c>
       <c r="C44">
-        <v>1169.280015482609</v>
+        <v>1169.280015429352</v>
       </c>
       <c r="D44">
-        <v>1169.280032106591</v>
+        <v>1169.280018233996</v>
       </c>
       <c r="E44">
-        <v>1169.279999972303</v>
+        <v>1169.279999983989</v>
       </c>
       <c r="F44">
-        <v>1812.712741483914</v>
+        <v>1812.712741113013</v>
       </c>
       <c r="G44">
-        <v>2741.135096212526</v>
+        <v>2741.135096035043</v>
       </c>
       <c r="H44">
-        <v>3028.089398854867</v>
+        <v>3028.089398350082</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -5138,22 +5138,22 @@
         <v>22</v>
       </c>
       <c r="C45">
-        <v>7574.400013580597</v>
+        <v>7574.400013533345</v>
       </c>
       <c r="D45">
-        <v>7574.40002818589</v>
+        <v>7574.400016000782</v>
       </c>
       <c r="E45">
-        <v>7574.399999961674</v>
+        <v>7574.399999977722</v>
       </c>
       <c r="F45">
-        <v>11724.68879912081</v>
+        <v>10734.19021641575</v>
       </c>
       <c r="G45">
-        <v>15420.16350008815</v>
+        <v>11441.52165524776</v>
       </c>
       <c r="H45">
-        <v>15753.0727923597</v>
+        <v>12484.89161184485</v>
       </c>
     </row>
   </sheetData>
